--- a/StudentData.xlsx
+++ b/StudentData.xlsx
@@ -6,13 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Student Details" r:id="rId3" sheetId="1"/>
+    <sheet name="Studenti" r:id="rId3" sheetId="1"/>
+    <sheet name="Histograma note" r:id="rId4" sheetId="2"/>
+    <sheet name="Semigrupe" r:id="rId5" sheetId="3"/>
+    <sheet name="Statistici semigrupe" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="43">
   <si>
     <t>Numar matricol</t>
   </si>
@@ -26,6 +29,9 @@
     <t>Formatie de studiu</t>
   </si>
   <si>
+    <t>Nota</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
     <t>I73/9</t>
   </si>
   <si>
+    <t>fara nota</t>
+  </si>
+  <si>
     <t>129</t>
   </si>
   <si>
@@ -111,6 +120,30 @@
   </si>
   <si>
     <t>Olteanu</t>
+  </si>
+  <si>
+    <t>Numar studenti</t>
+  </si>
+  <si>
+    <t>Histograma</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Media generala</t>
+  </si>
+  <si>
+    <t>Semigrupa</t>
+  </si>
+  <si>
+    <t>Semigrupa 1</t>
+  </si>
+  <si>
+    <t>Semigrupa 2</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -155,13 +188,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="8.25" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="7.3515625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="16.0859375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="8.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -177,24 +211,318 @@
       <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>7.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>8</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="13.4375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.53515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.16796875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>6.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="8.25" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.3515625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.0859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.23828125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>9</v>
@@ -205,10 +533,16 @@
       <c r="D3" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="E3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>13</v>
@@ -219,75 +553,251 @@
       <c r="D4" t="s" s="0">
         <v>15</v>
       </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>7</v>
+      <c r="F5" t="n" s="0">
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>6.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>9.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>7.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.53515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.16796875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>7.333333333333333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/StudentData.xlsx
+++ b/StudentData.xlsx
@@ -7,15 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Studenti" r:id="rId3" sheetId="1"/>
-    <sheet name="Histograma note" r:id="rId4" sheetId="2"/>
-    <sheet name="Semigrupe" r:id="rId5" sheetId="3"/>
-    <sheet name="Statistici semigrupe" r:id="rId6" sheetId="4"/>
+    <sheet name="Semigrupe" r:id="rId4" sheetId="2"/>
+    <sheet name="Statistici semigrupe" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
   <si>
     <t>Numar matricol</t>
   </si>
@@ -89,7 +88,7 @@
     <t>I73/9</t>
   </si>
   <si>
-    <t>fara nota</t>
+    <t>-</t>
   </si>
   <si>
     <t>129</t>
@@ -122,28 +121,19 @@
     <t>Olteanu</t>
   </si>
   <si>
+    <t>Semigrupa</t>
+  </si>
+  <si>
+    <t>Semigrupa 1</t>
+  </si>
+  <si>
+    <t>Semigrupa 2</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Numar studenti</t>
-  </si>
-  <si>
-    <t>Histograma</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Media generala</t>
-  </si>
-  <si>
-    <t>Semigrupa</t>
-  </si>
-  <si>
-    <t>Semigrupa 1</t>
-  </si>
-  <si>
-    <t>Semigrupa 2</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -190,13 +180,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="13.546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="8.25" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="7.3515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.0859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="8.23828125" customWidth="true" bestFit="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -358,108 +341,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="13.4375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.53515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.16796875" customWidth="true" bestFit="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C1" t="s" s="0">
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
         <v>36</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="0">
+      <c r="B2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F2" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C2" t="s" s="0">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
         <v>37</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="B3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C3" t="s" s="0">
+      <c r="B6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>37</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C4" t="s" s="0">
+      <c r="B7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
         <v>37</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="B5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C5" t="s" s="0">
+      <c r="B8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
         <v>37</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n" s="0">
-        <v>7.0</v>
-      </c>
-      <c r="B6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="B7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="B8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B10" t="n" s="0">
-        <v>6.0</v>
+      <c r="B9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -469,220 +531,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="8.25" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.3515625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.0859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="8.23828125" customWidth="true" bestFit="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n" s="0">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F4" t="n" s="0">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F5" t="n" s="0">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F6" t="n" s="0">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n" s="0">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n" s="0">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.53515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.16796875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n" s="0">
         <v>5.0</v>
@@ -693,10 +552,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -706,9 +562,6 @@
       <c r="B4" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n" s="0">
@@ -717,9 +570,6 @@
       <c r="B5" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n" s="0">
@@ -728,9 +578,6 @@
       <c r="B6" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n" s="0">
@@ -739,18 +586,15 @@
       <c r="B7" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C7" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>7.333333333333333</v>
@@ -761,10 +605,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -774,9 +615,6 @@
       <c r="B13" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C13" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n" s="0">
@@ -785,9 +623,6 @@
       <c r="B14" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="C14" t="s" s="0">
-        <v>37</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n" s="0">
@@ -795,9 +630,6 @@
       </c>
       <c r="B15" t="n" s="0">
         <v>1.0</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
